--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МИХНЕВИ ТРАНС ЕООД/МИХНЕВИ ТРАНС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МИХНЕВИ ТРАНС ЕООД/МИХНЕВИ ТРАНС ЕООД.xlsx
@@ -169,7 +169,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -972,7 +972,7 @@
         <v>6</v>
       </c>
       <c r="D13" s="7">
-        <v>1.5933</v>
+        <v>1.59328</v>
       </c>
       <c r="E13" s="6">
         <v>875.3</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МИХНЕВИ ТРАНС ЕООД/МИХНЕВИ ТРАНС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МИХНЕВИ ТРАНС ЕООД/МИХНЕВИ ТРАНС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="50">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -560,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -573,13 +576,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -622,160 +625,172 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>200</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>1.54</v>
+        <v>1.499</v>
       </c>
       <c r="I2" s="1">
-        <v>308</v>
+        <v>1.539</v>
       </c>
       <c r="J2">
+        <v>307.8</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.61</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>322</v>
       </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2">
         <v>806020</v>
       </c>
-      <c r="N2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>85.89</v>
       </c>
       <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3">
+        <v>1.499</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.539</v>
+      </c>
+      <c r="J3">
+        <v>132.18471</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="L3" s="1">
+        <v>140.0007</v>
+      </c>
+      <c r="M3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4">
+        <v>59.524</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4">
+        <v>1.564</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.594</v>
+      </c>
+      <c r="J4">
+        <v>94.88125599999999</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L4" s="1">
+        <v>100.00032</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
         <v>29</v>
-      </c>
-      <c r="H3">
-        <v>1.54</v>
-      </c>
-      <c r="I3" s="1">
-        <v>132.27</v>
-      </c>
-      <c r="J3">
-        <v>1.63</v>
-      </c>
-      <c r="K3" s="1">
-        <v>140</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4">
-        <v>59.52</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4">
-        <v>1.59</v>
-      </c>
-      <c r="I4" s="1">
-        <v>94.64</v>
-      </c>
-      <c r="J4">
-        <v>1.68</v>
-      </c>
-      <c r="K4" s="1">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="L4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5">
         <v>1.32</v>
@@ -789,151 +804,163 @@
       <c r="K5" s="1">
         <v>1.32</v>
       </c>
-      <c r="L5" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>1.32</v>
+      </c>
+      <c r="M5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6">
+        <v>63.959</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6">
+        <v>1.619</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.649</v>
+      </c>
+      <c r="J6">
+        <v>105.468391</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.72</v>
+      </c>
+      <c r="L6" s="1">
+        <v>110.00948</v>
+      </c>
+      <c r="M6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7">
+        <v>62.863</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7">
+        <v>1.619</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.649</v>
+      </c>
+      <c r="J7">
+        <v>103.661087</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L7" s="1">
+        <v>110.01025</v>
+      </c>
+      <c r="M7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
         <v>27</v>
       </c>
-      <c r="F6">
-        <v>63.96</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6">
-        <v>1.65</v>
-      </c>
-      <c r="I6" s="1">
-        <v>105.53</v>
-      </c>
-      <c r="J6">
-        <v>1.72</v>
-      </c>
-      <c r="K6" s="1">
-        <v>110.01</v>
-      </c>
-      <c r="L6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6">
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8">
+        <v>77.143</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8">
+        <v>1.674</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.704</v>
+      </c>
+      <c r="J8">
+        <v>131.451672</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L8" s="1">
+        <v>135.00025</v>
+      </c>
+      <c r="M8" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7">
-        <v>62.86</v>
-      </c>
-      <c r="G7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7">
-        <v>1.65</v>
-      </c>
-      <c r="I7" s="1">
-        <v>103.72</v>
-      </c>
-      <c r="J7">
-        <v>1.75</v>
-      </c>
-      <c r="K7" s="1">
-        <v>110</v>
-      </c>
-      <c r="L7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8">
-        <v>77.14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>1.7</v>
-      </c>
-      <c r="I8" s="1">
-        <v>131.14</v>
-      </c>
-      <c r="J8">
-        <v>1.75</v>
-      </c>
-      <c r="K8" s="1">
-        <v>135</v>
-      </c>
-      <c r="L8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -941,49 +968,49 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" s="6">
-        <v>549.37</v>
+        <v>549.379</v>
       </c>
       <c r="C13" s="6">
         <v>6</v>
       </c>
       <c r="D13" s="7">
-        <v>1.59328</v>
+        <v>1.593521</v>
       </c>
       <c r="E13" s="6">
-        <v>875.3</v>
+        <v>875.45</v>
       </c>
       <c r="F13" s="6">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>917.02</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="6">
         <v>1</v>
@@ -1001,22 +1028,22 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="9">
-        <v>550.37</v>
+        <v>550.379</v>
       </c>
       <c r="C15" s="9">
         <v>7</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="9">
-        <v>876.62</v>
+        <v>876.77</v>
       </c>
       <c r="F15" s="9">
-        <v>918.3200000000001</v>
+        <v>918.34</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/МИХНЕВИ ТРАНС ЕООД/МИХНЕВИ ТРАНС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/МИХНЕВИ ТРАНС ЕООД/МИХНЕВИ ТРАНС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="49">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -171,8 +168,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -265,10 +262,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -576,13 +573,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -625,172 +622,160 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>200</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2">
-        <v>1.499</v>
+        <v>1.539</v>
       </c>
       <c r="I2" s="1">
-        <v>1.539</v>
+        <v>307.8</v>
       </c>
       <c r="J2">
-        <v>307.8</v>
+        <v>1.61</v>
       </c>
       <c r="K2" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L2" s="1">
         <v>322</v>
       </c>
-      <c r="M2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2">
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2">
         <v>806020</v>
       </c>
-      <c r="O2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
       </c>
       <c r="F3">
         <v>85.89</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H3">
-        <v>1.499</v>
+        <v>1.539</v>
       </c>
       <c r="I3" s="1">
-        <v>1.539</v>
+        <v>132.185</v>
       </c>
       <c r="J3">
-        <v>132.18471</v>
+        <v>1.63</v>
       </c>
       <c r="K3" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L3" s="1">
-        <v>140.0007</v>
-      </c>
-      <c r="M3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3">
+        <v>140.001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
       </c>
       <c r="F4">
         <v>59.524</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H4">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I4" s="1">
-        <v>1.594</v>
+        <v>94.881</v>
       </c>
       <c r="J4">
-        <v>94.88125599999999</v>
+        <v>1.68</v>
       </c>
       <c r="K4" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L4" s="1">
-        <v>100.00032</v>
-      </c>
-      <c r="M4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5">
         <v>1.32</v>
@@ -804,163 +789,151 @@
       <c r="K5" s="1">
         <v>1.32</v>
       </c>
-      <c r="L5" s="1">
-        <v>1.32</v>
-      </c>
-      <c r="M5" t="s">
-        <v>34</v>
-      </c>
-      <c r="N5">
+      <c r="L5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
         <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
       </c>
       <c r="F6">
         <v>63.959</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H6">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I6" s="1">
-        <v>1.649</v>
+        <v>105.468</v>
       </c>
       <c r="J6">
-        <v>105.468391</v>
+        <v>1.72</v>
       </c>
       <c r="K6" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L6" s="1">
-        <v>110.00948</v>
-      </c>
-      <c r="M6" t="s">
-        <v>35</v>
-      </c>
-      <c r="N6">
+        <v>110.009</v>
+      </c>
+      <c r="L6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
         <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
       </c>
       <c r="F7">
         <v>62.863</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I7" s="1">
-        <v>1.649</v>
+        <v>103.661</v>
       </c>
       <c r="J7">
-        <v>103.661087</v>
+        <v>1.75</v>
       </c>
       <c r="K7" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L7" s="1">
-        <v>110.01025</v>
-      </c>
-      <c r="M7" t="s">
-        <v>36</v>
-      </c>
-      <c r="N7">
+        <v>110.01</v>
+      </c>
+      <c r="L7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
         <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
       </c>
       <c r="F8">
         <v>77.143</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I8" s="1">
-        <v>1.704</v>
+        <v>131.452</v>
       </c>
       <c r="J8">
-        <v>131.451672</v>
+        <v>1.75</v>
       </c>
       <c r="K8" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L8" s="1">
-        <v>135.00025</v>
-      </c>
-      <c r="M8" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8">
+        <v>135</v>
+      </c>
+      <c r="L8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
+      <c r="N8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="3" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -968,69 +941,69 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14">
       <c r="A12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="6">
         <v>549.379</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <v>6</v>
       </c>
       <c r="D13" s="7">
-        <v>1.593521</v>
-      </c>
-      <c r="E13" s="6">
-        <v>875.45</v>
-      </c>
-      <c r="F13" s="6">
+        <v>1.594</v>
+      </c>
+      <c r="E13" s="7">
+        <v>875.447</v>
+      </c>
+      <c r="F13" s="7">
         <v>917.02</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:14">
       <c r="A14" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="6">
         <v>1</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>1</v>
       </c>
       <c r="D14" s="7">
         <v>1.32</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>1.32</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="7">
         <v>1.32</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:14">
       <c r="A15" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="9">
         <v>550.379</v>
@@ -1040,7 +1013,7 @@
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="9">
-        <v>876.77</v>
+        <v>876.7670000000001</v>
       </c>
       <c r="F15" s="9">
         <v>918.34</v>
